--- a/hiring_companies_2026-10-24.xlsx
+++ b/hiring_companies_2026-10-24.xlsx
@@ -477,7 +477,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sightpath Medical</t>
+          <t>Backbone Media</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -492,12 +492,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>IT System Support Engineer</t>
+          <t>Media Coordinator - Paid Social</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/8403048734533834470</t>
+          <t>https://jooble.org/jdp/3982665225841222874</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -507,7 +507,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Sightpath+Medical</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Backbone+Media</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -524,7 +524,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sightpath Medical</t>
+          <t>Backbone Media</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>IT System Support Engineer</t>
+          <t>Media Coordinator - Paid Social</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/8403048734533834470</t>
+          <t>https://jooble.org/jdp/3982665225841222874</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Sightpath+Medical</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Backbone+Media</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -571,7 +571,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Rula Health</t>
+          <t>Backbone Media</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -586,12 +586,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Licensed Clinical Psychologist (No Associates) - Remote</t>
+          <t>Media Coordinator - Paid Social</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-7297816496250385200</t>
+          <t>https://jooble.org/jdp/3982665225841222874</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Rula+Health</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Backbone+Media</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -618,7 +618,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sightpath Medical</t>
+          <t>Backbone Media</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>IT System Support Engineer</t>
+          <t>Media Coordinator - Paid Social</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/8403048734533834470</t>
+          <t>https://jooble.org/jdp/3982665225841222874</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Sightpath+Medical</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Backbone+Media</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -665,7 +665,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sightpath Medical</t>
+          <t>Backbone Media</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -680,12 +680,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>IT System Support Engineer</t>
+          <t>Media Coordinator - Paid Social</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/8403048734533834470</t>
+          <t>https://jooble.org/jdp/3982665225841222874</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Sightpath+Medical</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Backbone+Media</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -712,7 +712,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sightpath Medical</t>
+          <t>Backbone Media</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -727,12 +727,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>IT System Support Engineer</t>
+          <t>Media Coordinator - Paid Social</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/8403048734533834470</t>
+          <t>https://jooble.org/jdp/3982665225841222874</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Sightpath+Medical</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Backbone+Media</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -759,12 +759,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>iMerit Technology</t>
+          <t>Iris Software Inc.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Remote (Worldwide)</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -774,22 +774,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AI Trainer - Video Annotation</t>
+          <t>Lead Full Stack Python Developer ( 100 % Remote )</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://remotive.com/remote-jobs/artificial-intelligence/ai-trainer-video-annotation-2091161</t>
+          <t>https://jooble.org/jdp/-7978106078642769563</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=iMerit+Technology</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Iris+Software+Inc.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -799,19 +799,19 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>job link live</t>
+          <t>job link unknown</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Hawaii Public Radio</t>
+          <t>Iris Software Inc.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -821,12 +821,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Digital News Producer</t>
+          <t>Lead Full Stack Python Developer ( 100 % Remote )</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-1742648343992155582</t>
+          <t>https://jooble.org/jdp/-7978106078642769563</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Hawaii+Public+Radio</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Iris+Software+Inc.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -853,12 +853,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hawaii Public Radio</t>
+          <t>Iris Software Inc.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -868,12 +868,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Digital News Producer</t>
+          <t>Lead Full Stack Python Developer ( 100 % Remote )</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-1742648343992155582</t>
+          <t>https://jooble.org/jdp/-7978106078642769563</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Hawaii+Public+Radio</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Iris+Software+Inc.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -900,12 +900,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sightpath Medical</t>
+          <t>Iris Software Inc.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>IT System Support Engineer</t>
+          <t>Lead Full Stack Python Developer ( 100 % Remote )</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/8403048734533834470</t>
+          <t>https://jooble.org/jdp/-778033137951289538</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Sightpath+Medical</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Iris+Software+Inc.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -947,12 +947,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Hawaii Public Radio</t>
+          <t>Iris Software Inc.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -962,12 +962,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Digital News Producer</t>
+          <t>Lead Full Stack Python Developer ( 100 % Remote )</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-1742648343992155582</t>
+          <t>https://jooble.org/jdp/-1389481908051802245</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Hawaii+Public+Radio</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Iris+Software+Inc.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -994,12 +994,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Hawaii Public Radio</t>
+          <t>Iris Software Inc.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Digital News Producer</t>
+          <t>Lead Full Stack Python Developer ( 100 % Remote )</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-1742648343992155582</t>
+          <t>https://jooble.org/jdp/-778033137951289538</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Hawaii+Public+Radio</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Iris+Software+Inc.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Hawaii Public Radio</t>
+          <t>Mars Men</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Digital News Producer</t>
+          <t>Senior Web Designer</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-1742648343992155582</t>
+          <t>https://jooble.org/jdp/-4470930341229003265</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Hawaii+Public+Radio</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Mars+Men</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1088,12 +1088,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Hilton Grand Vacations</t>
+          <t>Mars Men</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Remote Timeshare Sales Executive</t>
+          <t>Senior Web Designer</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3515275133057304502</t>
+          <t>https://jooble.org/jdp/-4470930341229003265</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Hilton+Grand+Vacations</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Mars+Men</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1135,12 +1135,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Hilton Grand Vacations</t>
+          <t>Mars Men</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Remote Timeshare Sales Executive</t>
+          <t>Senior Web Designer</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3515275133057304502</t>
+          <t>https://jooble.org/jdp/-4470930341229003265</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Hilton+Grand+Vacations</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Mars+Men</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1182,12 +1182,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Hawaii Public Radio</t>
+          <t>Mars Men</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Digital News Producer</t>
+          <t>Senior Web Designer</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-1742648343992155582</t>
+          <t>https://jooble.org/jdp/-4470930341229003265</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Hawaii+Public+Radio</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Mars+Men</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1229,12 +1229,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Hilton Grand Vacations</t>
+          <t>Mars Men</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1244,12 +1244,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Remote Timeshare Sales Executive</t>
+          <t>Senior Web Designer</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3515275133057304502</t>
+          <t>https://jooble.org/jdp/-4470930341229003265</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Hilton+Grand+Vacations</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Mars+Men</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1276,12 +1276,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Hilton Grand Vacations</t>
+          <t>Mars Men</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1291,12 +1291,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Remote Timeshare Sales Executive</t>
+          <t>Senior Web Designer</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3515275133057304502</t>
+          <t>https://jooble.org/jdp/-4470930341229003265</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Hilton+Grand+Vacations</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Mars+Men</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1323,12 +1323,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Hilton Grand Vacations</t>
+          <t>Iverson Inc.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1338,12 +1338,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Remote Timeshare Sales Executive</t>
+          <t>Web Designer</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3515275133057304502</t>
+          <t>https://jooble.org/jdp/-418271960183469473</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Hilton+Grand+Vacations</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Iverson+Inc.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1370,12 +1370,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Jamdanceacademy</t>
+          <t>Lago</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-4306974034244588307</t>
+          <t>https://jooble.org/jdp/3995264790951728818</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Jamdanceacademy</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Lago</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1417,12 +1417,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jamdanceacademy</t>
+          <t>Lago</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-4306974034244588307</t>
+          <t>https://jooble.org/jdp/3995264790951728818</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Jamdanceacademy</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Lago</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1464,12 +1464,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Hilton Grand Vacations</t>
+          <t>Lago</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1479,12 +1479,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Remote Timeshare Sales Executive</t>
+          <t>Web Designer</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3515275133057304502</t>
+          <t>https://jooble.org/jdp/3995264790951728818</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Hilton+Grand+Vacations</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Lago</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1511,12 +1511,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jamdanceacademy</t>
+          <t>Iverson Inc.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-4306974034244588307</t>
+          <t>https://jooble.org/jdp/-418271960183469473</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Jamdanceacademy</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Iverson+Inc.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1558,12 +1558,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Jamdanceacademy</t>
+          <t>Lago</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-4306974034244588307</t>
+          <t>https://jooble.org/jdp/3995264790951728818</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Jamdanceacademy</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Lago</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1605,12 +1605,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Jamdanceacademy</t>
+          <t>Lago</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-4306974034244588307</t>
+          <t>https://jooble.org/jdp/3995264790951728818</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Jamdanceacademy</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Lago</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1652,12 +1652,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Glitch Productions</t>
+          <t>Iverson Inc.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Head of Marketing</t>
+          <t>Web Designer</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-1896309345003592366</t>
+          <t>https://jooble.org/jdp/-418271960183469473</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Glitch+Productions</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Iverson+Inc.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1699,12 +1699,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Glitch Productions</t>
+          <t>Iverson Inc.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Head of Marketing</t>
+          <t>Web Designer</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-1896309345003592366</t>
+          <t>https://jooble.org/jdp/-418271960183469473</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Glitch+Productions</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Iverson+Inc.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1746,12 +1746,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jamdanceacademy</t>
+          <t>Iverson Inc.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-4306974034244588307</t>
+          <t>https://jooble.org/jdp/-418271960183469473</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Jamdanceacademy</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Iverson+Inc.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1793,12 +1793,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Glitch Productions</t>
+          <t>Lago</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Head of Marketing</t>
+          <t>Web Designer</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-1896309345003592366</t>
+          <t>https://jooble.org/jdp/3995264790951728818</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Glitch+Productions</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Lago</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1840,12 +1840,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Glitch Productions</t>
+          <t>Iverson Inc.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1855,12 +1855,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Head of Marketing</t>
+          <t>Web Designer</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-1896309345003592366</t>
+          <t>https://jooble.org/jdp/-418271960183469473</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Glitch+Productions</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Iverson+Inc.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1887,12 +1887,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Glitch Productions</t>
+          <t>kozmetickesluzby.vecnakraska.sk - Jobboard</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Head of Marketing</t>
+          <t>Remote Freelance Graphic &amp; Web Designer (20-30 hrs/mo)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-1896309345003592366</t>
+          <t>https://jooble.org/jdp/7842717937893207677</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Glitch+Productions</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=kozmetickesluzby.vecnakraska.sk+-+Jobboard</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1934,12 +1934,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1Password</t>
+          <t>kozmetickesluzby.vecnakraska.sk - Jobboard</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Developer Intern, Front-End Platform - Winter 2027</t>
+          <t>Remote Freelance Graphic &amp; Web Designer (20-30 hrs/mo)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/8194126000353593621</t>
+          <t>https://jooble.org/jdp/7842717937893207677</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=1Password</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=kozmetickesluzby.vecnakraska.sk+-+Jobboard</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1981,12 +1981,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1Password</t>
+          <t>kozmetickesluzby.vecnakraska.sk - Jobboard</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Developer Intern, Front-End Platform - Winter 2027</t>
+          <t>Remote Freelance Graphic &amp; Web Designer (20-30 hrs/mo)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/8194126000353593621</t>
+          <t>https://jooble.org/jdp/7842717937893207677</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=1Password</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=kozmetickesluzby.vecnakraska.sk+-+Jobboard</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2028,12 +2028,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Glitch Productions</t>
+          <t>kozmetickesluzby.vecnakraska.sk - Jobboard</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2043,12 +2043,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Head of Marketing</t>
+          <t>Remote Freelance Graphic &amp; Web Designer (20-30 hrs/mo)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-1896309345003592366</t>
+          <t>https://jooble.org/jdp/7842717937893207677</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Glitch+Productions</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=kozmetickesluzby.vecnakraska.sk+-+Jobboard</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2075,12 +2075,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1Password</t>
+          <t>kozmetickesluzby.vecnakraska.sk - Jobboard</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2090,12 +2090,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Developer Intern, Front-End Platform - Winter 2027</t>
+          <t>Remote Freelance Graphic &amp; Web Designer (20-30 hrs/mo)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/8194126000353593621</t>
+          <t>https://jooble.org/jdp/7842717937893207677</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=1Password</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=kozmetickesluzby.vecnakraska.sk+-+Jobboard</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2122,12 +2122,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1Password</t>
+          <t>kozmetickesluzby.vecnakraska.sk - Jobboard</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Developer Intern, Front-End Platform - Winter 2027</t>
+          <t>Remote Freelance Graphic &amp; Web Designer (20-30 hrs/mo)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/8194126000353593621</t>
+          <t>https://jooble.org/jdp/7842717937893207677</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=1Password</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=kozmetickesluzby.vecnakraska.sk+-+Jobboard</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2169,12 +2169,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1Password</t>
+          <t>Adequo</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>.NET Developer, SaaS Manager | Developer Intern, Extension Excellence - Winter 2027 | Developer Intern, Front-End Platform - Winter 2027 | Frontend Developer, Device Security | Performance Marketing M</t>
+          <t>Remote Web Designer for Digital Products &amp; Brand Systems</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/8194126000353593621</t>
+          <t>https://jooble.org/jdp/-2492723370407682753</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=1Password</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Adequo</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2216,12 +2216,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Adequo</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>News Reporter</t>
+          <t>Remote Web Designer for Digital Products &amp; Brand Systems</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6902517382483435260</t>
+          <t>https://jooble.org/jdp/-2492723370407682753</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Northeastern+University</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Adequo</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2263,12 +2263,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Adequo</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>News Reporter</t>
+          <t>Remote Web Designer for Digital Products &amp; Brand Systems</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6902517382483435260</t>
+          <t>https://jooble.org/jdp/-2492723370407682753</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Northeastern+University</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Adequo</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2310,12 +2310,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1Password</t>
+          <t>Adequo</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Developer Intern, Front-End Platform - Winter 2027</t>
+          <t>Remote Web Designer for Digital Products &amp; Brand Systems</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/8194126000353593621</t>
+          <t>https://jooble.org/jdp/-2492723370407682753</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=1Password</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Adequo</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2357,12 +2357,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Adequo</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>News Reporter</t>
+          <t>Remote Web Designer for Digital Products &amp; Brand Systems</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6902517382483435260</t>
+          <t>https://jooble.org/jdp/-2492723370407682753</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Northeastern+University</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Adequo</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2404,12 +2404,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Adequo</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2419,12 +2419,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>News Reporter</t>
+          <t>Remote Web Designer for Digital Products &amp; Brand Systems</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6902517382483435260</t>
+          <t>https://jooble.org/jdp/-2492723370407682753</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Northeastern+University</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Adequo</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2451,12 +2451,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Kee Group Marketing</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2466,12 +2466,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>News Reporter</t>
+          <t>Part-Time Web and Graphic Designer</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6902517382483435260</t>
+          <t>https://jooble.org/jdp/-6763115104913740248</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Northeastern+University</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Kee+Group+Marketing</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2498,12 +2498,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Wm Bolthouse Farms Inc</t>
+          <t>Theoria Creative</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2513,12 +2513,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Influencer Marketing Coordinator</t>
+          <t>Senior Brand &amp; Web Designer — Remote, Part-Time (Biotech)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-4206387976728994704</t>
+          <t>https://jooble.org/jdp/6088905054285441446</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Wm+Bolthouse+Farms+Inc</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Theoria+Creative</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2545,12 +2545,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Wm Bolthouse Farms Inc</t>
+          <t>Theoria Creative</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Influencer Marketing Coordinator</t>
+          <t>Senior Brand &amp; Web Designer — Remote, Part-Time (Biotech)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-4206387976728994704</t>
+          <t>https://jooble.org/jdp/6088905054285441446</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Wm+Bolthouse+Farms+Inc</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Theoria+Creative</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2592,12 +2592,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Theoria Creative</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>News Reporter</t>
+          <t>Senior Brand &amp; Web Designer — Remote, Part-Time (Biotech)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6902517382483435260</t>
+          <t>https://jooble.org/jdp/6088905054285441446</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Northeastern+University</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Theoria+Creative</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2639,12 +2639,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Wm Bolthouse Farms Inc</t>
+          <t>Theoria Creative</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2654,12 +2654,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Influencer Marketing Coordinator</t>
+          <t>Senior Brand &amp; Web Designer — Remote, Part-Time (Biotech)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-4206387976728994704</t>
+          <t>https://jooble.org/jdp/6088905054285441446</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Wm+Bolthouse+Farms+Inc</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Theoria+Creative</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2686,12 +2686,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Wm Bolthouse Farms Inc</t>
+          <t>Kee Group Marketing</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Influencer Marketing Coordinator</t>
+          <t>Part-Time Web and Graphic Designer</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-4206387976728994704</t>
+          <t>https://jooble.org/jdp/-6763115104913740248</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Wm+Bolthouse+Farms+Inc</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Kee+Group+Marketing</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2733,12 +2733,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Wm Bolthouse Farms Inc</t>
+          <t>Theoria Creative</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Influencer Marketing Coordinator</t>
+          <t>Senior Brand &amp; Web Designer — Remote, Part-Time (Biotech)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-4206387976728994704</t>
+          <t>https://jooble.org/jdp/6088905054285441446</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Wm+Bolthouse+Farms+Inc</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Theoria+Creative</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2780,12 +2780,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Lehrer Family Chiropractic</t>
+          <t>Kee Group Marketing</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Remote Health Writer</t>
+          <t>Part-Time Web and Graphic Designer</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/4181488994687400297</t>
+          <t>https://jooble.org/jdp/-6763115104913740248</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Lehrer+Family+Chiropractic</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Kee+Group+Marketing</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
